--- a/SuppXLS/Scen_SYS_CarbonBudget_Sector.xlsx
+++ b/SuppXLS/Scen_SYS_CarbonBudget_Sector.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olex\Documents\MANRID\ResLab\Modelling\TIMES\TIMES-IE\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\Integrated saturation V1.1\AFOLU model\tim-leaf v1.0\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF18B8F9-36B2-4868-B09F-38EEA1339FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36F059F-26CE-40D9-9162-D17597F4F6F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3045" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="-16310" windowWidth="29020" windowHeight="15700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="24" r:id="rId1"/>
@@ -1324,9 +1324,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1364,9 +1364,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1399,26 +1399,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1451,26 +1434,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1646,20 +1612,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43ACE639-45BB-4BC0-8EFB-335579A1276F}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="10" width="8.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="1" max="4" width="21.7265625" customWidth="1"/>
+    <col min="5" max="6" width="14.1796875" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" customWidth="1"/>
+    <col min="8" max="10" width="8.1796875" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" customWidth="1"/>
+    <col min="12" max="12" width="8.1796875" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="13.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A1" s="18"/>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -1687,7 +1653,7 @@
       <c r="Y1" s="19"/>
       <c r="Z1" s="19"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
@@ -1715,7 +1681,7 @@
       <c r="Y2" s="19"/>
       <c r="Z2" s="19"/>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1743,7 +1709,7 @@
       <c r="Y3" s="19"/>
       <c r="Z3" s="19"/>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A4" s="18"/>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -1771,7 +1737,7 @@
       <c r="Y4" s="19"/>
       <c r="Z4" s="19"/>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A5" s="18"/>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -1799,7 +1765,7 @@
       <c r="Y5" s="19"/>
       <c r="Z5" s="19"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A6" s="18"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -1827,7 +1793,7 @@
       <c r="Y6" s="19"/>
       <c r="Z6" s="19"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -1855,7 +1821,7 @@
       <c r="Y7" s="19"/>
       <c r="Z7" s="19"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -1883,7 +1849,7 @@
       <c r="Y8" s="19"/>
       <c r="Z8" s="19"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -1911,7 +1877,7 @@
       <c r="Y9" s="19"/>
       <c r="Z9" s="19"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -1939,7 +1905,7 @@
       <c r="Y10" s="19"/>
       <c r="Z10" s="19"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -1967,7 +1933,7 @@
       <c r="Y11" s="19"/>
       <c r="Z11" s="19"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -1995,7 +1961,7 @@
       <c r="Y12" s="19"/>
       <c r="Z12" s="19"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -2023,7 +1989,7 @@
       <c r="Y13" s="19"/>
       <c r="Z13" s="19"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -2051,7 +2017,7 @@
       <c r="Y14" s="19"/>
       <c r="Z14" s="19"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -2079,7 +2045,7 @@
       <c r="Y15" s="19"/>
       <c r="Z15" s="19"/>
     </row>
-    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="102.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="34" t="s">
         <v>88</v>
       </c>
@@ -2109,7 +2075,7 @@
       <c r="Y16" s="19"/>
       <c r="Z16" s="19"/>
     </row>
-    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="22"/>
@@ -2137,7 +2103,7 @@
       <c r="Y17" s="19"/>
       <c r="Z17" s="19"/>
     </row>
-    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -2165,7 +2131,7 @@
       <c r="Y18" s="19"/>
       <c r="Z18" s="19"/>
     </row>
-    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="25" t="s">
         <v>89</v>
       </c>
@@ -2197,7 +2163,7 @@
       <c r="Y19" s="19"/>
       <c r="Z19" s="19"/>
     </row>
-    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="25" t="s">
         <v>90</v>
       </c>
@@ -2229,7 +2195,7 @@
       <c r="Y20" s="19"/>
       <c r="Z20" s="19"/>
     </row>
-    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>91</v>
       </c>
@@ -2261,7 +2227,7 @@
       <c r="Y21" s="19"/>
       <c r="Z21" s="19"/>
     </row>
-    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="25"/>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
@@ -2289,7 +2255,7 @@
       <c r="Y22" s="19"/>
       <c r="Z22" s="19"/>
     </row>
-    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="25" t="s">
         <v>92</v>
       </c>
@@ -2321,7 +2287,7 @@
       <c r="Y23" s="19"/>
       <c r="Z23" s="19"/>
     </row>
-    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="25"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -2349,7 +2315,7 @@
       <c r="Y24" s="19"/>
       <c r="Z24" s="19"/>
     </row>
-    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="25"/>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -2377,7 +2343,7 @@
       <c r="Y25" s="19"/>
       <c r="Z25" s="19"/>
     </row>
-    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>93</v>
       </c>
@@ -2409,7 +2375,7 @@
       <c r="Y26" s="19"/>
       <c r="Z26" s="19"/>
     </row>
-    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="25"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
@@ -2437,7 +2403,7 @@
       <c r="Y27" s="19"/>
       <c r="Z27" s="19"/>
     </row>
-    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="25"/>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -2465,7 +2431,7 @@
       <c r="Y28" s="19"/>
       <c r="Z28" s="19"/>
     </row>
-    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="25" t="s">
         <v>94</v>
       </c>
@@ -2497,7 +2463,7 @@
       <c r="Y29" s="19"/>
       <c r="Z29" s="19"/>
     </row>
-    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>95</v>
       </c>
@@ -2529,7 +2495,7 @@
       <c r="Y30" s="19"/>
       <c r="Z30" s="19"/>
     </row>
-    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="25" t="s">
         <v>97</v>
       </c>
@@ -2561,7 +2527,7 @@
       <c r="Y31" s="19"/>
       <c r="Z31" s="19"/>
     </row>
-    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="31"/>
       <c r="B32" s="32" t="s">
         <v>99</v>
@@ -2591,7 +2557,7 @@
       <c r="Y32" s="19"/>
       <c r="Z32" s="19"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A33" s="18"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
@@ -2619,7 +2585,7 @@
       <c r="Y33" s="19"/>
       <c r="Z33" s="19"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A34" s="18"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
@@ -2647,7 +2613,7 @@
       <c r="Y34" s="19"/>
       <c r="Z34" s="19"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A35" s="18"/>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
@@ -2675,7 +2641,7 @@
       <c r="Y35" s="19"/>
       <c r="Z35" s="19"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A36" s="18"/>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
@@ -2703,7 +2669,7 @@
       <c r="Y36" s="19"/>
       <c r="Z36" s="19"/>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A37" s="18"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
@@ -2731,7 +2697,7 @@
       <c r="Y37" s="19"/>
       <c r="Z37" s="19"/>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A38" s="18"/>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -2759,7 +2725,7 @@
       <c r="Y38" s="19"/>
       <c r="Z38" s="19"/>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A39" s="18"/>
       <c r="B39" s="18"/>
       <c r="C39" s="18"/>
@@ -2787,7 +2753,7 @@
       <c r="Y39" s="19"/>
       <c r="Z39" s="19"/>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A40" s="18"/>
       <c r="B40" s="18"/>
       <c r="C40" s="18"/>
@@ -2815,7 +2781,7 @@
       <c r="Y40" s="19"/>
       <c r="Z40" s="19"/>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A41" s="18"/>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -2843,7 +2809,7 @@
       <c r="Y41" s="19"/>
       <c r="Z41" s="19"/>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A42" s="18"/>
       <c r="B42" s="18"/>
       <c r="C42" s="18"/>
@@ -2871,7 +2837,7 @@
       <c r="Y42" s="19"/>
       <c r="Z42" s="19"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A43" s="19"/>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
@@ -2899,7 +2865,7 @@
       <c r="Y43" s="19"/>
       <c r="Z43" s="19"/>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A44" s="19"/>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -2927,7 +2893,7 @@
       <c r="Y44" s="19"/>
       <c r="Z44" s="19"/>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A45" s="19"/>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -2955,7 +2921,7 @@
       <c r="Y45" s="19"/>
       <c r="Z45" s="19"/>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A46" s="19"/>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -2983,7 +2949,7 @@
       <c r="Y46" s="19"/>
       <c r="Z46" s="19"/>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A47" s="19"/>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
@@ -3011,7 +2977,7 @@
       <c r="Y47" s="19"/>
       <c r="Z47" s="19"/>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A48" s="19"/>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
@@ -3039,7 +3005,7 @@
       <c r="Y48" s="19"/>
       <c r="Z48" s="19"/>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" s="19"/>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -3067,7 +3033,7 @@
       <c r="Y49" s="19"/>
       <c r="Z49" s="19"/>
     </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A50" s="19"/>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -3095,7 +3061,7 @@
       <c r="Y50" s="19"/>
       <c r="Z50" s="19"/>
     </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" s="19"/>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
@@ -3123,7 +3089,7 @@
       <c r="Y51" s="19"/>
       <c r="Z51" s="19"/>
     </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" s="19"/>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -3151,7 +3117,7 @@
       <c r="Y52" s="19"/>
       <c r="Z52" s="19"/>
     </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" s="19"/>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -3179,7 +3145,7 @@
       <c r="Y53" s="19"/>
       <c r="Z53" s="19"/>
     </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" s="19"/>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -3207,7 +3173,7 @@
       <c r="Y54" s="19"/>
       <c r="Z54" s="19"/>
     </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A55" s="19"/>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -3235,7 +3201,7 @@
       <c r="Y55" s="19"/>
       <c r="Z55" s="19"/>
     </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="19"/>
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
@@ -3263,7 +3229,7 @@
       <c r="Y56" s="19"/>
       <c r="Z56" s="19"/>
     </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="19"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -3291,7 +3257,7 @@
       <c r="Y57" s="19"/>
       <c r="Z57" s="19"/>
     </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="19"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -3319,7 +3285,7 @@
       <c r="Y58" s="19"/>
       <c r="Z58" s="19"/>
     </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="19"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -3347,7 +3313,7 @@
       <c r="Y59" s="19"/>
       <c r="Z59" s="19"/>
     </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="19"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -3375,7 +3341,7 @@
       <c r="Y60" s="19"/>
       <c r="Z60" s="19"/>
     </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A61" s="19"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -3403,7 +3369,7 @@
       <c r="Y61" s="19"/>
       <c r="Z61" s="19"/>
     </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" s="19"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
@@ -3431,7 +3397,7 @@
       <c r="Y62" s="19"/>
       <c r="Z62" s="19"/>
     </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" s="19"/>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
@@ -3459,7 +3425,7 @@
       <c r="Y63" s="19"/>
       <c r="Z63" s="19"/>
     </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" s="19"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -3487,7 +3453,7 @@
       <c r="Y64" s="19"/>
       <c r="Z64" s="19"/>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A65" s="19"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -3515,7 +3481,7 @@
       <c r="Y65" s="19"/>
       <c r="Z65" s="19"/>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A66" s="19"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
@@ -3543,7 +3509,7 @@
       <c r="Y66" s="19"/>
       <c r="Z66" s="19"/>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A67" s="19"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
@@ -3571,7 +3537,7 @@
       <c r="Y67" s="19"/>
       <c r="Z67" s="19"/>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A68" s="19"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
@@ -3599,7 +3565,7 @@
       <c r="Y68" s="19"/>
       <c r="Z68" s="19"/>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A69" s="19"/>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -3627,7 +3593,7 @@
       <c r="Y69" s="19"/>
       <c r="Z69" s="19"/>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A70" s="19"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
@@ -3655,7 +3621,7 @@
       <c r="Y70" s="19"/>
       <c r="Z70" s="19"/>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A71" s="19"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
@@ -3683,7 +3649,7 @@
       <c r="Y71" s="19"/>
       <c r="Z71" s="19"/>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A72" s="19"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
@@ -3711,7 +3677,7 @@
       <c r="Y72" s="19"/>
       <c r="Z72" s="19"/>
     </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A73" s="19"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -3739,7 +3705,7 @@
       <c r="Y73" s="19"/>
       <c r="Z73" s="19"/>
     </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A74" s="19"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
@@ -3767,7 +3733,7 @@
       <c r="Y74" s="19"/>
       <c r="Z74" s="19"/>
     </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A75" s="19"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
@@ -3795,7 +3761,7 @@
       <c r="Y75" s="19"/>
       <c r="Z75" s="19"/>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A76" s="19"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
@@ -3823,7 +3789,7 @@
       <c r="Y76" s="19"/>
       <c r="Z76" s="19"/>
     </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A77" s="19"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
@@ -3851,7 +3817,7 @@
       <c r="Y77" s="19"/>
       <c r="Z77" s="19"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A78" s="19"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
@@ -3879,7 +3845,7 @@
       <c r="Y78" s="19"/>
       <c r="Z78" s="19"/>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A79" s="19"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
@@ -3907,7 +3873,7 @@
       <c r="Y79" s="19"/>
       <c r="Z79" s="19"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A80" s="19"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
@@ -3935,7 +3901,7 @@
       <c r="Y80" s="19"/>
       <c r="Z80" s="19"/>
     </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A81" s="19"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -3963,7 +3929,7 @@
       <c r="Y81" s="19"/>
       <c r="Z81" s="19"/>
     </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -3991,7 +3957,7 @@
       <c r="Y82" s="19"/>
       <c r="Z82" s="19"/>
     </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A83" s="19"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
@@ -4019,7 +3985,7 @@
       <c r="Y83" s="19"/>
       <c r="Z83" s="19"/>
     </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A84" s="19"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
@@ -4047,7 +4013,7 @@
       <c r="Y84" s="19"/>
       <c r="Z84" s="19"/>
     </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A85" s="19"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
@@ -4075,7 +4041,7 @@
       <c r="Y85" s="19"/>
       <c r="Z85" s="19"/>
     </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A86" s="19"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -4103,7 +4069,7 @@
       <c r="Y86" s="19"/>
       <c r="Z86" s="19"/>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A87" s="19"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
@@ -4131,7 +4097,7 @@
       <c r="Y87" s="19"/>
       <c r="Z87" s="19"/>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A88" s="19"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
@@ -4159,7 +4125,7 @@
       <c r="Y88" s="19"/>
       <c r="Z88" s="19"/>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A89" s="19"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -4187,7 +4153,7 @@
       <c r="Y89" s="19"/>
       <c r="Z89" s="19"/>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A90" s="19"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
@@ -4215,7 +4181,7 @@
       <c r="Y90" s="19"/>
       <c r="Z90" s="19"/>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A91" s="19"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
@@ -4243,7 +4209,7 @@
       <c r="Y91" s="19"/>
       <c r="Z91" s="19"/>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A92" s="19"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
@@ -4271,7 +4237,7 @@
       <c r="Y92" s="19"/>
       <c r="Z92" s="19"/>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A93" s="19"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
@@ -4299,7 +4265,7 @@
       <c r="Y93" s="19"/>
       <c r="Z93" s="19"/>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A94" s="19"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
@@ -4327,7 +4293,7 @@
       <c r="Y94" s="19"/>
       <c r="Z94" s="19"/>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A95" s="19"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
@@ -4355,7 +4321,7 @@
       <c r="Y95" s="19"/>
       <c r="Z95" s="19"/>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A96" s="19"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
@@ -4383,7 +4349,7 @@
       <c r="Y96" s="19"/>
       <c r="Z96" s="19"/>
     </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A97" s="19"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
@@ -4411,7 +4377,7 @@
       <c r="Y97" s="19"/>
       <c r="Z97" s="19"/>
     </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A98" s="19"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
@@ -4439,7 +4405,7 @@
       <c r="Y98" s="19"/>
       <c r="Z98" s="19"/>
     </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A99" s="19"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
@@ -4491,39 +4457,39 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C030FF-C503-4743-9DBD-437AEB1E949D}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.54296875" customWidth="1"/>
+    <col min="25" max="25" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.1796875" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="C3" s="1" t="str" cm="1">
         <f t="array" ref="C3">IF(LEFT(INDEX(C5:C7,$A$4),1)&lt;&gt;"*",INDEX(C5:C7,$A$4),"")</f>
         <v>IE</v>
@@ -4637,12 +4603,12 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -4757,7 +4723,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -4874,7 +4840,7 @@
         <v>*IE-MN</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -4991,7 +4957,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
         <v>32</v>
       </c>
@@ -4999,7 +4965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
@@ -5007,7 +4973,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>35</v>
       </c>
@@ -5015,7 +4981,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>36</v>
       </c>
@@ -5023,7 +4989,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
@@ -5031,7 +4997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
@@ -5039,7 +5005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
@@ -5047,7 +5013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5021,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
@@ -5063,7 +5029,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
@@ -5071,7 +5037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
@@ -5079,7 +5045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
@@ -5087,7 +5053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>45</v>
       </c>
@@ -5095,7 +5061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>46</v>
       </c>
@@ -5103,7 +5069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>47</v>
       </c>
@@ -5111,7 +5077,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>48</v>
       </c>
@@ -5119,7 +5085,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>49</v>
       </c>
@@ -5127,7 +5093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
         <v>50</v>
       </c>
@@ -5135,7 +5101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>51</v>
       </c>
@@ -5143,7 +5109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>52</v>
       </c>
@@ -5151,7 +5117,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>53</v>
       </c>
@@ -5159,7 +5125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>54</v>
       </c>
@@ -5167,7 +5133,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>55</v>
       </c>
@@ -5175,7 +5141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>56</v>
       </c>
@@ -5183,7 +5149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
         <v>57</v>
       </c>
@@ -5191,7 +5157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>58</v>
       </c>
@@ -5199,7 +5165,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>59</v>
       </c>
@@ -5207,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>60</v>
       </c>
@@ -5252,21 +5218,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011941A8-04BF-45E8-9F60-D4E07475AB4A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B3:D13"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>103</v>
       </c>
@@ -5274,7 +5240,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>109</v>
       </c>
@@ -5285,7 +5251,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>110</v>
       </c>
@@ -5296,7 +5262,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>157</v>
       </c>
@@ -5307,7 +5273,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>158</v>
       </c>
@@ -5318,7 +5284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>111</v>
       </c>
@@ -5329,7 +5295,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>112</v>
       </c>
@@ -5340,12 +5306,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>295</v>
       </c>
@@ -5363,43 +5329,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9318C9B-7F0A-410C-BCB5-F22D93E1F454}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.36328125" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
+    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.08984375" customWidth="1"/>
+    <col min="12" max="12" width="33.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="str">
         <f>"~UC_Sets: R_E: "  &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!C3)</f>
         <v>~UC_Sets: R_E: IE</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H4" t="str">
         <f>IF(RIGHT(B2,1)&lt;&gt;" ","~UC_T","")</f>
         <v>~UC_T</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="10" t="s">
         <v>61</v>
       </c>
@@ -5434,7 +5401,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7" t="s">
         <v>69</v>
       </c>
@@ -5451,7 +5418,7 @@
       </c>
       <c r="L6" s="13"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>135</v>
       </c>
@@ -5481,7 +5448,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>78</v>
       </c>
@@ -5499,7 +5466,7 @@
       </c>
       <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>136</v>
       </c>
@@ -5529,7 +5496,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>78</v>
       </c>
@@ -5547,7 +5514,7 @@
       </c>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>137</v>
       </c>
@@ -5577,7 +5544,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>138</v>
       </c>
@@ -5607,7 +5574,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>139</v>
       </c>
@@ -5637,7 +5604,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>140</v>
       </c>
@@ -5667,7 +5634,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>141</v>
       </c>
@@ -5697,7 +5664,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>142</v>
       </c>
@@ -5727,7 +5694,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>143</v>
       </c>
@@ -5757,7 +5724,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>144</v>
       </c>
@@ -5797,43 +5764,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EC2971-91FC-4261-B0BB-58C7F43C1746}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.453125" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="str">
         <f>"~UC_Sets: R_S: " &amp; _xlfn.TEXTJOIN(",",TRUE,Regions!D3:AD3)</f>
         <v>~UC_Sets: R_S: National,IE-CW,IE-D,IE-KE,IE-KK,IE-LS,IE-LD,IE-LH,IE-MH,IE-OY,IE-WH,IE-WX,IE-WW,IE-CE,IE-CO,IE-KY,IE-LK,IE-TA,IE-WD,IE-G,IE-LM,IE-MO,IE-RN,IE-SO,IE-CN,IE-DL,IE-MN</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H4" t="str">
         <f>IF(RIGHT(B2,1)&lt;&gt;" ","~UC_T","")</f>
         <v>~UC_T</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="10" t="s">
         <v>61</v>
       </c>
@@ -5868,7 +5835,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="7" t="s">
         <v>69</v>
       </c>
@@ -5885,7 +5852,7 @@
       </c>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>105</v>
       </c>
@@ -5915,7 +5882,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
         <v>78</v>
       </c>
@@ -5933,7 +5900,7 @@
       </c>
       <c r="K8" s="17"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>107</v>
       </c>
@@ -5963,7 +5930,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
         <v>78</v>
       </c>
@@ -5981,7 +5948,7 @@
       </c>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>114</v>
       </c>
@@ -6011,7 +5978,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>121</v>
       </c>
@@ -6041,7 +6008,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>118</v>
       </c>
@@ -6071,7 +6038,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>122</v>
       </c>
@@ -6101,7 +6068,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>119</v>
       </c>
@@ -6131,7 +6098,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>123</v>
       </c>
@@ -6161,7 +6128,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>120</v>
       </c>
@@ -6191,7 +6158,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>124</v>
       </c>
@@ -6232,20 +6199,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2314F01-B0DB-448B-9217-DEB90E2D1CCA}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B2" s="14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="15" t="s">
         <v>83</v>
       </c>
@@ -6270,7 +6237,7 @@
         <v>National</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C4" s="8" t="s">
         <v>85</v>
       </c>
